--- a/LISTAS_ORDENADAS/MA/Soportes y escuadras/SOPORTE DE ESTANTE.xlsx
+++ b/LISTAS_ORDENADAS/MA/Soportes y escuadras/SOPORTE DE ESTANTE.xlsx
@@ -810,16 +810,11 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="10" t="n">
-        <v>45216.53897530344</v>
+        <v>45266</v>
       </c>
       <c r="F1" s="23" t="n"/>
       <c r="G1" s="23" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="28" t="inlineStr">
         <is>
@@ -855,19 +850,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
@@ -899,7 +881,7 @@
       </c>
       <c r="C26" s="26" t="n"/>
       <c r="D26" s="9" t="n">
-        <v>4175.49</v>
+        <v>3450.825</v>
       </c>
       <c r="I26" s="4" t="n"/>
     </row>
@@ -916,7 +898,7 @@
       </c>
       <c r="C27" s="26" t="n"/>
       <c r="D27" s="9" t="n">
-        <v>5225.75</v>
+        <v>4318.805</v>
       </c>
       <c r="I27" s="4" t="n"/>
     </row>
@@ -933,7 +915,7 @@
       </c>
       <c r="C28" s="26" t="n"/>
       <c r="D28" s="9" t="n">
-        <v>6800.27</v>
+        <v>5620.065</v>
       </c>
       <c r="I28" s="4" t="n"/>
     </row>
@@ -950,7 +932,7 @@
       </c>
       <c r="C29" s="26" t="n"/>
       <c r="D29" s="9" t="n">
-        <v>9608.92</v>
+        <v>7941.257</v>
       </c>
       <c r="I29" s="4" t="n"/>
     </row>
@@ -967,7 +949,7 @@
       </c>
       <c r="C30" s="26" t="n"/>
       <c r="D30" s="9" t="n">
-        <v>14162.29</v>
+        <v>11704.373</v>
       </c>
       <c r="I30" s="4" t="n"/>
     </row>
@@ -984,7 +966,7 @@
       </c>
       <c r="C31" s="26" t="n"/>
       <c r="D31" s="9" t="n">
-        <v>19473.14</v>
+        <v>16093.505</v>
       </c>
       <c r="I31" s="4" t="n"/>
     </row>
@@ -1001,7 +983,7 @@
       </c>
       <c r="C32" s="26" t="n"/>
       <c r="D32" s="19" t="n">
-        <v>25034.23</v>
+        <v>20689.449</v>
       </c>
       <c r="I32" s="4" t="n"/>
     </row>
@@ -1036,7 +1018,7 @@
       </c>
       <c r="C34" s="26" t="n"/>
       <c r="D34" s="9" t="n">
-        <v>4175.49</v>
+        <v>3450.825</v>
       </c>
     </row>
     <row r="35" ht="19.5" customHeight="1">
@@ -1052,7 +1034,7 @@
       </c>
       <c r="C35" s="26" t="n"/>
       <c r="D35" s="9" t="n">
-        <v>5225.75</v>
+        <v>4318.805</v>
       </c>
     </row>
     <row r="36" ht="19.5" customHeight="1">
@@ -1068,7 +1050,7 @@
       </c>
       <c r="C36" s="26" t="n"/>
       <c r="D36" s="9" t="n">
-        <v>6800.27</v>
+        <v>5620.065</v>
       </c>
     </row>
     <row r="37" ht="19.5" customHeight="1">
@@ -1084,7 +1066,7 @@
       </c>
       <c r="C37" s="26" t="n"/>
       <c r="D37" s="9" t="n">
-        <v>9608.92</v>
+        <v>7941.257</v>
       </c>
     </row>
     <row r="38" ht="19.5" customHeight="1">
@@ -1100,7 +1082,7 @@
       </c>
       <c r="C38" s="26" t="n"/>
       <c r="D38" s="9" t="n">
-        <v>14162.29</v>
+        <v>11704.373</v>
       </c>
     </row>
     <row r="39" ht="19.5" customHeight="1">
@@ -1116,7 +1098,7 @@
       </c>
       <c r="C39" s="26" t="n"/>
       <c r="D39" s="9" t="n">
-        <v>19473.14</v>
+        <v>16093.505</v>
       </c>
     </row>
     <row r="40" ht="19.5" customHeight="1">
@@ -1132,16 +1114,12 @@
       </c>
       <c r="C40" s="27" t="n"/>
       <c r="D40" s="9" t="n">
-        <v>25034.23</v>
-      </c>
-    </row>
-    <row r="41"/>
-    <row r="42"/>
+        <v>20689.449</v>
+      </c>
+    </row>
     <row r="43" ht="20.25" customHeight="1">
       <c r="B43" s="6" t="n"/>
     </row>
-    <row r="44"/>
-    <row r="45"/>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
@@ -1168,26 +1146,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B40:C40"/>
     <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A10:E10"/>
     <mergeCell ref="A11:E11"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
